--- a/artfynd/A 1251-2022 artfynd.xlsx
+++ b/artfynd/A 1251-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121092084</v>
       </c>
       <c r="B2" t="n">
-        <v>56552</v>
+        <v>56555</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>121383906</v>
       </c>
       <c r="B3" t="n">
-        <v>58025</v>
+        <v>58028</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>121383905</v>
       </c>
       <c r="B4" t="n">
-        <v>57782</v>
+        <v>57785</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 1251-2022 artfynd.xlsx
+++ b/artfynd/A 1251-2022 artfynd.xlsx
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121383906</v>
+        <v>121383905</v>
       </c>
       <c r="B3" t="n">
-        <v>58028</v>
+        <v>57785</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,30 +811,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>102999</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -923,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121383905</v>
+        <v>121383906</v>
       </c>
       <c r="B4" t="n">
-        <v>57785</v>
+        <v>58028</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,30 +935,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102999</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>

--- a/artfynd/A 1251-2022 artfynd.xlsx
+++ b/artfynd/A 1251-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121092084</v>
       </c>
       <c r="B2" t="n">
-        <v>56555</v>
+        <v>56558</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>121383905</v>
       </c>
       <c r="B3" t="n">
-        <v>57785</v>
+        <v>57788</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>121383906</v>
       </c>
       <c r="B4" t="n">
-        <v>58028</v>
+        <v>58031</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 1251-2022 artfynd.xlsx
+++ b/artfynd/A 1251-2022 artfynd.xlsx
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121383905</v>
+        <v>121383906</v>
       </c>
       <c r="B3" t="n">
-        <v>57788</v>
+        <v>58031</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,30 +811,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102999</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -923,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121383906</v>
+        <v>121383905</v>
       </c>
       <c r="B4" t="n">
-        <v>58031</v>
+        <v>57788</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,30 +935,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>102999</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>

--- a/artfynd/A 1251-2022 artfynd.xlsx
+++ b/artfynd/A 1251-2022 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>121383906</v>
       </c>
       <c r="B3" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>121383905</v>
       </c>
       <c r="B4" t="n">
-        <v>57788</v>
+        <v>57789</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 1251-2022 artfynd.xlsx
+++ b/artfynd/A 1251-2022 artfynd.xlsx
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121383906</v>
+        <v>121383905</v>
       </c>
       <c r="B3" t="n">
-        <v>58032</v>
+        <v>57790</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,30 +811,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>102999</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -923,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121383905</v>
+        <v>121383906</v>
       </c>
       <c r="B4" t="n">
-        <v>57789</v>
+        <v>58033</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,30 +935,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102999</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>

--- a/artfynd/A 1251-2022 artfynd.xlsx
+++ b/artfynd/A 1251-2022 artfynd.xlsx
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121383905</v>
+        <v>121383906</v>
       </c>
       <c r="B3" t="n">
-        <v>57790</v>
+        <v>58033</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,30 +811,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102999</v>
+        <v>103044</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -923,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121383906</v>
+        <v>121383905</v>
       </c>
       <c r="B4" t="n">
-        <v>58033</v>
+        <v>57790</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,30 +935,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>102999</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>

--- a/artfynd/A 1251-2022 artfynd.xlsx
+++ b/artfynd/A 1251-2022 artfynd.xlsx
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121383906</v>
+        <v>121383905</v>
       </c>
       <c r="B3" t="n">
-        <v>58033</v>
+        <v>57790</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,30 +811,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103044</v>
+        <v>102999</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -923,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121383905</v>
+        <v>121383906</v>
       </c>
       <c r="B4" t="n">
-        <v>57790</v>
+        <v>58033</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,30 +935,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102999</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>

--- a/artfynd/A 1251-2022 artfynd.xlsx
+++ b/artfynd/A 1251-2022 artfynd.xlsx
@@ -1050,7 +1050,7 @@
         <v>131058100</v>
       </c>
       <c r="B5" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 1251-2022 artfynd.xlsx
+++ b/artfynd/A 1251-2022 artfynd.xlsx
@@ -1050,7 +1050,7 @@
         <v>131058100</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>57728</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 1251-2022 artfynd.xlsx
+++ b/artfynd/A 1251-2022 artfynd.xlsx
@@ -1050,7 +1050,7 @@
         <v>131058100</v>
       </c>
       <c r="B5" t="n">
-        <v>57728</v>
+        <v>57729</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 1251-2022 artfynd.xlsx
+++ b/artfynd/A 1251-2022 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>121092084</v>
       </c>
       <c r="B2" t="n">
-        <v>56558</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -799,15 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121383905</v>
+        <v>131058100</v>
       </c>
       <c r="B3" t="n">
-        <v>57791</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57794</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,21 +805,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102999</v>
+        <v>102621</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -881,22 +871,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,42 +913,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121383906</v>
+        <v>121383905</v>
       </c>
       <c r="B4" t="n">
-        <v>58034</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58393</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>102999</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -1047,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131058100</v>
+        <v>121383906</v>
       </c>
       <c r="B5" t="n">
-        <v>57729</v>
+        <v>58636</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1058,16 +1043,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102621</v>
+        <v>103044</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1077,7 +1062,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1124,22 +1109,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2024-11-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2024-11-28</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 1251-2022 artfynd.xlsx
+++ b/artfynd/A 1251-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121092084</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131058100</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1029,6 +1044,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121383905</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1148,8 +1168,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121383906</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>